--- a/SPC26S1 - 06 June v2.xlsx
+++ b/SPC26S1 - 06 June v2.xlsx
@@ -2519,7 +2519,7 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down list, and anything not on the list is rejected so a typo cannot slip in. To add a new status, edit the list under Data &gt; Data Validation.</t>
   </si>
   <si>
     <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
@@ -2729,7 +2729,7 @@
     <t>Call ins to get bar code letter if needed and insights on denials</t>
   </si>
   <si>
-    <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+    <t>Statuses on the drop-down: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
   <si>
     <t>134 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
@@ -2738,7 +2738,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 19</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">    5 - No limit on file: 15</t>
   </si>
   <si>
-    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds every claim for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>Awaiting resolution on claim #556349314 (DOS 01/27/2026) before reprocessing</t>
@@ -7910,8 +7910,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A34" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12797,8 +12797,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A43" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14947,8 +14947,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A17" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17982,8 +17982,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A25" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20111,8 +20111,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20140,8 +20140,9 @@
       <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>574</v>
+      <c r="A3" s="9" t="str">
+        <f>COUNTA(BH!$D$2:$D$1000,DME!$D$2:$D$1000,GAE!$D$2:$D$1000,ORTHO!$D$2:$D$1000,US!$D$2:$D$1000)&amp;" claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US."</f>
+        <v>133 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -20163,28 +20164,33 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>577</v>
+      <c r="A8" s="9" t="str">
+        <f>"    1 - Due in 5 days or less: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;=0",BH!$L$2:$L$1000,"&lt;=5"),COUNTIFS(DME!$L$2:$L$1000,"&gt;=0",DME!$L$2:$L$1000,"&lt;=5"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;=0",GAE!$L$2:$L$1000,"&lt;=5"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;=0",ORTHO!$L$2:$L$1000,"&lt;=5"),COUNTIFS(US!$L$2:$L$1000,"&gt;=0",US!$L$2:$L$1000,"&lt;=5"))</f>
+        <v>    1 - Due in 5 days or less: 1</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>578</v>
+      <c r="A9" s="9" t="str">
+        <f>"    2 - Due in 6-30 days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;5",BH!$L$2:$L$1000,"&lt;=30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;5",DME!$L$2:$L$1000,"&lt;=30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;5",GAE!$L$2:$L$1000,"&lt;=30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;5",ORTHO!$L$2:$L$1000,"&lt;=30"),COUNTIFS(US!$L$2:$L$1000,"&gt;5",US!$L$2:$L$1000,"&lt;=30"))</f>
+        <v>    2 - Due in 6-30 days: 7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>579</v>
+      <c r="A10" s="9" t="str">
+        <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
+        <v>    3 - Due in 31+ days: 34</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>580</v>
+      <c r="A11" s="9" t="str">
+        <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
+        <v>    4 - Past deadline: 76</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>581</v>
+      <c r="A12" s="9" t="str">
+        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <v>    5 - No limit on file: 15</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">

--- a/SPC26S1 - 06 June v2.xlsx
+++ b/SPC26S1 - 06 June v2.xlsx
@@ -2968,7 +2968,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="103">
+  <dxfs count="104">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3967,9 +3967,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFF9933"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3991,6 +3995,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7900,7 +7911,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -12787,7 +12801,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="21">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="22">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -14937,7 +14954,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -17972,7 +17992,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -20101,7 +20124,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -20125,7 +20151,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -20354,14 +20380,14 @@
     <row r="45" spans="1:1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Under Review - orange</t>
+          <t xml:space="preserve">    Under Review - bright orange, bold (follow up on these)</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Denied - red</t>
+          <t xml:space="preserve">    Denied, not worked yet (Latest Date Worked empty) - red</t>
         </is>
       </c>
     </row>
@@ -20381,6 +20407,13 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied, already worked (Latest Date Worked filled in) - light pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Any other status is left unshaded.</t>
         </is>
@@ -20427,6 +20460,11 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="expression" dxfId="103" priority="9">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SPC26S1 - 06 June v2.xlsx
+++ b/SPC26S1 - 06 June v2.xlsx
@@ -2738,7 +2738,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically; Finalized claims with a Latest Date Worked have their deadline cells left empty and are not counted):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 19</t>
@@ -4505,14 +4505,15 @@
         <v>10</v>
       </c>
       <c r="M2" s="11" t="str">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N2" s="11" t="str">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,10,15))</f>
         <v>46310</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -4612,14 +4613,15 @@
         <v>-21</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>120</v>
       </c>
       <c r="N3" s="11">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>305</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,9,14))</f>
         <v>46279</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -4719,14 +4721,15 @@
         <v>-15</v>
       </c>
       <c r="M4" s="11" t="str">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N4" s="11" t="str">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -4822,14 +4825,15 @@
         <v>240</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>290</v>
       </c>
       <c r="N5" s="11">
-        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+120-TODAY()))</f>
         <v>45</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,6,2))</f>
         <v>46540</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -4925,14 +4929,15 @@
         <v>243</v>
       </c>
       <c r="M6" s="11" t="str">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N6" s="11" t="str">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2027,6,5))</f>
         <v>46543</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -5028,14 +5033,15 @@
         <v>247</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>291</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+120-TODAY()))</f>
         <v>46</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2027,6,9))</f>
         <v>46547</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -5133,14 +5139,15 @@
         <v>248</v>
       </c>
       <c r="M8" s="11">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>291</v>
       </c>
       <c r="N8" s="11">
-        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+120-TODAY()))</f>
         <v>46</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2027,6,10))</f>
         <v>46548</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -5238,14 +5245,15 @@
         <v>257</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>290</v>
       </c>
       <c r="N9" s="11">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+120-TODAY()))</f>
         <v>45</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2027,6,19))</f>
         <v>46557</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -5341,14 +5349,15 @@
         <v>264</v>
       </c>
       <c r="M10" s="11" t="str">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N10" s="11" t="str">
-        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2027,6,26))</f>
         <v>46564</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -5444,14 +5453,15 @@
         <v>267</v>
       </c>
       <c r="M11" s="11">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>290</v>
       </c>
       <c r="N11" s="11">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+120-TODAY()))</f>
         <v>45</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -5547,14 +5557,15 @@
         <v>268</v>
       </c>
       <c r="M12" s="11" t="str">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N12" s="11" t="str">
-        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2027,6,30))</f>
         <v>46568</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -6082,7 +6093,7 @@
       </c>
       <c r="M18" s="11"/>
       <c r="N18" s="11" t="str">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O18" s="6"/>
@@ -6432,14 +6443,15 @@
         <v>-33</v>
       </c>
       <c r="M22" s="11">
-        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($F22="","",$F22+90-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="N22" s="11">
-        <f ca="1">IF($C22="","",$C22+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+540-TODAY()))</f>
         <v>465</v>
       </c>
       <c r="O22" s="6">
+        <f>IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",DATE(2026,9,2))</f>
         <v>46267</v>
       </c>
       <c r="P22" s="5" t="s">
@@ -6547,14 +6559,15 @@
         <v>-28</v>
       </c>
       <c r="M23" s="11">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+365-TODAY()))</f>
         <v>296</v>
       </c>
       <c r="N23" s="11">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+365-TODAY()))</f>
         <v>296</v>
       </c>
       <c r="O23" s="6">
+        <f>IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",DATE(2026,9,7))</f>
         <v>46272</v>
       </c>
       <c r="P23" s="5" t="s">
@@ -6656,14 +6669,15 @@
         <v>-27</v>
       </c>
       <c r="M24" s="11">
-        <f ca="1">IF($C24="","",$C24+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="N24" s="11">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="O24" s="6">
+        <f>IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",DATE(2026,9,8))</f>
         <v>46273</v>
       </c>
       <c r="P24" s="5" t="s">
@@ -6765,14 +6779,15 @@
         <v>-21</v>
       </c>
       <c r="M25" s="11" t="str">
-        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N25" s="11" t="str">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O25" s="6">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2026,9,14))</f>
         <v>46279</v>
       </c>
       <c r="P25" s="5" t="s">
@@ -6872,14 +6887,15 @@
         <v>-19</v>
       </c>
       <c r="M26" s="11" t="str">
-        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N26" s="11" t="str">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O26" s="6">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P26" s="5" t="s">
@@ -6979,14 +6995,15 @@
         <v>-13</v>
       </c>
       <c r="M27" s="11">
-        <f ca="1">IF($F27="","",$F27+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($F27="","",$F27+90-TODAY()))</f>
         <v>-13</v>
       </c>
       <c r="N27" s="11" t="str">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O27" s="6">
+        <f>IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",DATE(2026,9,22))</f>
         <v>46287</v>
       </c>
       <c r="P27" s="5" t="s">
@@ -7086,14 +7103,15 @@
         <v>-12</v>
       </c>
       <c r="M28" s="11" t="str">
-        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N28" s="11" t="str">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O28" s="6">
+        <f>IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P28" s="5" t="s">
@@ -7195,14 +7213,15 @@
         <v>-12</v>
       </c>
       <c r="M29" s="11">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
         <v>324</v>
       </c>
       <c r="N29" s="11">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
         <v>324</v>
       </c>
       <c r="O29" s="6">
+        <f>IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P29" s="5" t="s">
@@ -7306,14 +7325,15 @@
         <v>-8</v>
       </c>
       <c r="M30" s="11">
-        <f ca="1">IF($F30="","",$F30+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($F30="","",$F30+90-TODAY()))</f>
         <v>-8</v>
       </c>
       <c r="N30" s="11">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
         <v>332</v>
       </c>
       <c r="O30" s="6">
+        <f>IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P30" s="5" t="s">
@@ -7414,20 +7434,21 @@
       <c r="K31" s="3">
         <v>46284</v>
       </c>
-      <c r="L31" s="11">
+      <c t="str" r="L31" s="11">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
-        <v>-32</v>
-      </c>
-      <c r="M31" s="11">
-        <f ca="1">IF($F31="","",$F31+90-TODAY())</f>
-        <v>-32</v>
-      </c>
-      <c r="N31" s="11">
-        <f ca="1">IF($C31="","",$C31+540-TODAY())</f>
-        <v>465</v>
-      </c>
-      <c r="O31" s="6">
-        <v>46268</v>
+        <v/>
+      </c>
+      <c t="str" r="M31" s="11">
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($F31="","",$F31+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N31" s="11">
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+540-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O31" s="6">
+        <f>IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",DATE(2026,9,3))</f>
+        <v/>
       </c>
       <c r="P31" s="5" t="s">
         <v>45</v>
@@ -7527,20 +7548,21 @@
       <c r="K32" s="3">
         <v>46283</v>
       </c>
-      <c r="L32" s="11">
+      <c t="str" r="L32" s="11">
         <f ca="1">IF($O32="","",$O32-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M32" s="11">
-        <f ca="1">IF($F32="","",$F32+90-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="N32" s="11">
-        <f ca="1">IF($C32="","",$C32+365-TODAY())</f>
-        <v>303</v>
-      </c>
-      <c r="O32" s="6">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M32" s="11">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($F32="","",$F32+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N32" s="11">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O32" s="6">
+        <f>IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P32" s="5" t="s">
         <v>45</v>
@@ -7638,20 +7660,21 @@
       <c r="K33" s="3">
         <v>46300</v>
       </c>
-      <c r="L33" s="11">
+      <c t="str" r="L33" s="11">
         <f ca="1">IF($O33="","",$O33-TODAY())</f>
-        <v>-4</v>
-      </c>
-      <c r="M33" s="11">
-        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>330</v>
-      </c>
-      <c r="N33" s="11">
-        <f ca="1">IF($C33="","",$C33+90-TODAY())</f>
-        <v>55</v>
-      </c>
-      <c r="O33" s="6">
-        <v>46296</v>
+        <v/>
+      </c>
+      <c t="str" r="M33" s="11">
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N33" s="11">
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O33" s="6">
+        <f>IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",DATE(2026,10,1))</f>
+        <v/>
       </c>
       <c r="P33" s="5" t="s">
         <v>106</v>
@@ -7747,20 +7770,21 @@
       <c r="K34" s="3">
         <v>46293</v>
       </c>
-      <c r="L34" s="11">
+      <c t="str" r="L34" s="11">
         <f ca="1">IF($O34="","",$O34-TODAY())</f>
-        <v>-20</v>
-      </c>
-      <c r="M34" s="11">
-        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
-        <v>347</v>
-      </c>
-      <c r="N34" s="11">
-        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
-        <v>347</v>
-      </c>
-      <c r="O34" s="6">
-        <v>46280</v>
+        <v/>
+      </c>
+      <c t="str" r="M34" s="11">
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N34" s="11">
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O34" s="6">
+        <f>IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",DATE(2026,9,15))</f>
+        <v/>
       </c>
       <c r="P34" s="5" t="s">
         <v>45</v>
@@ -7826,100 +7850,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN34" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L34">
-    <cfRule type="expression" dxfId="94" priority="1">
+    <cfRule type="expression" dxfId="94" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="2">
+    <cfRule type="expression" dxfId="93" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="3">
+    <cfRule type="expression" dxfId="92" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="4">
+    <cfRule type="expression" dxfId="91" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="5">
+    <cfRule type="expression" dxfId="90" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M34">
-    <cfRule type="expression" dxfId="89" priority="6">
+    <cfRule type="expression" dxfId="89" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="7">
+    <cfRule type="expression" dxfId="88" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="8">
+    <cfRule type="expression" dxfId="87" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="9">
+    <cfRule type="expression" dxfId="86" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="10">
+    <cfRule type="expression" dxfId="85" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N34">
-    <cfRule type="expression" dxfId="84" priority="11">
+    <cfRule type="expression" dxfId="84" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="12">
+    <cfRule type="expression" dxfId="83" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="13">
+    <cfRule type="expression" dxfId="82" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="14">
+    <cfRule type="expression" dxfId="81" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="15">
+    <cfRule type="expression" dxfId="80" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O34">
-    <cfRule type="expression" dxfId="79" priority="16">
+    <cfRule type="expression" dxfId="79" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="17">
+    <cfRule type="expression" dxfId="78" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="18">
+    <cfRule type="expression" dxfId="77" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="19">
+    <cfRule type="expression" dxfId="76" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="20">
+    <cfRule type="expression" dxfId="75" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8132,14 +8161,15 @@
         <v>-32</v>
       </c>
       <c r="M2" s="11">
-        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($F2="","",$F2+90-TODAY()))</f>
         <v>-32</v>
       </c>
       <c r="N2" s="11" t="str">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,9,3))</f>
         <v>46268</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -8243,14 +8273,15 @@
         <v>-25</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+90-TODAY()))</f>
         <v>-25</v>
       </c>
       <c r="N3" s="11">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>269</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,9,10))</f>
         <v>46275</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -8354,14 +8385,15 @@
         <v>-20</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-20</v>
       </c>
       <c r="N4" s="11">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+180-TODAY()))</f>
         <v>105</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,9,15))</f>
         <v>46280</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -8467,14 +8499,15 @@
         <v>-15</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>84</v>
       </c>
       <c r="N5" s="11">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>269</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -8578,14 +8611,15 @@
         <v>-13</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>91</v>
       </c>
       <c r="N6" s="11">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,9,22))</f>
         <v>46287</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -8687,14 +8721,15 @@
         <v>55</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($F7="","",$F7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+365-TODAY()))</f>
         <v>240</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($F7="","",$F7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+365-TODAY()))</f>
         <v>240</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,11,29))</f>
         <v>46355</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -8794,14 +8829,15 @@
         <v>76</v>
       </c>
       <c r="M8" s="11">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+365-TODAY()))</f>
         <v>261</v>
       </c>
       <c r="N8" s="11">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+365-TODAY()))</f>
         <v>261</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,12,20))</f>
         <v>46376</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -8907,14 +8943,15 @@
         <v>242</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>253</v>
       </c>
       <c r="N9" s="11">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+120-TODAY()))</f>
         <v>8</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2027,6,4))</f>
         <v>46542</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -9016,14 +9053,15 @@
         <v>242</v>
       </c>
       <c r="M10" s="11">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="N10" s="11">
-        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+120-TODAY()))</f>
         <v>15</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2027,6,4))</f>
         <v>46542</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -9127,14 +9165,15 @@
         <v>243</v>
       </c>
       <c r="M11" s="11">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>282</v>
       </c>
       <c r="N11" s="11">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+120-TODAY()))</f>
         <v>37</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2027,6,5))</f>
         <v>46543</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -9234,14 +9273,15 @@
         <v>246</v>
       </c>
       <c r="M12" s="11" t="str">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N12" s="11" t="str">
-        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2027,6,8))</f>
         <v>46546</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -9337,14 +9377,15 @@
         <v>247</v>
       </c>
       <c r="M13" s="11" t="str">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N13" s="11" t="str">
-        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2027,6,9))</f>
         <v>46547</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -9442,14 +9483,15 @@
         <v>257</v>
       </c>
       <c r="M14" s="11">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="N14" s="11">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+120-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2027,6,19))</f>
         <v>46557</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -9555,14 +9597,15 @@
         <v>260</v>
       </c>
       <c r="M15" s="11">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="N15" s="11">
-        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+120-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2027,6,22))</f>
         <v>46560</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -9666,14 +9709,15 @@
         <v>260</v>
       </c>
       <c r="M16" s="11" t="str">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N16" s="11" t="str">
-        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2027,6,22))</f>
         <v>46560</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -9771,14 +9815,15 @@
         <v>260</v>
       </c>
       <c r="M17" s="11">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>333</v>
       </c>
       <c r="N17" s="11">
-        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+120-TODAY()))</f>
         <v>88</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2027,6,22))</f>
         <v>46560</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -9884,14 +9929,15 @@
         <v>262</v>
       </c>
       <c r="M18" s="11">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>274</v>
       </c>
       <c r="N18" s="11">
-        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+120-TODAY()))</f>
         <v>29</v>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2027,6,24))</f>
         <v>46562</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -9991,14 +10037,15 @@
         <v>264</v>
       </c>
       <c r="M19" s="11" t="str">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N19" s="11" t="str">
-        <f ca="1">IF($C19="","",$C19+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2027,6,26))</f>
         <v>46564</v>
       </c>
       <c r="P19" s="5" t="s">
@@ -10100,14 +10147,15 @@
         <v>267</v>
       </c>
       <c r="M20" s="11">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+365-TODAY()))</f>
         <v>284</v>
       </c>
       <c r="N20" s="11">
-        <f ca="1">IF($C20="","",$C20+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+120-TODAY()))</f>
         <v>39</v>
       </c>
       <c r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P20" s="5" t="s">
@@ -10209,14 +10257,15 @@
         <v>267</v>
       </c>
       <c r="M21" s="11">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+365-TODAY()))</f>
         <v>289</v>
       </c>
       <c r="N21" s="11">
-        <f ca="1">IF($C21="","",$C21+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+120-TODAY()))</f>
         <v>44</v>
       </c>
       <c r="O21" s="6">
+        <f>IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P21" s="5" t="s">
@@ -10506,14 +10555,15 @@
         <v>-41</v>
       </c>
       <c r="M24" s="11">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="N24" s="11">
-        <f ca="1">IF($C24="","",$C24+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+90-TODAY()))</f>
         <v>1</v>
       </c>
       <c r="O24" s="6">
+        <f>IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",DATE(2026,8,25))</f>
         <v>46259</v>
       </c>
       <c r="P24" s="5" t="s">
@@ -10621,14 +10671,15 @@
         <v>-28</v>
       </c>
       <c r="M25" s="11">
-        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+180-TODAY()))</f>
         <v>119</v>
       </c>
       <c r="N25" s="11">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+365-TODAY()))</f>
         <v>304</v>
       </c>
       <c r="O25" s="6">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2026,9,7))</f>
         <v>46272</v>
       </c>
       <c r="P25" s="5" t="s">
@@ -10736,14 +10787,15 @@
         <v>-19</v>
       </c>
       <c r="M26" s="11">
-        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+180-TODAY()))</f>
         <v>97</v>
       </c>
       <c r="N26" s="11">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
         <v>282</v>
       </c>
       <c r="O26" s="6">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P26" s="5" t="s">
@@ -10847,14 +10899,15 @@
         <v>-14</v>
       </c>
       <c r="M27" s="11">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="N27" s="11">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="O27" s="6">
+        <f>IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",DATE(2026,9,21))</f>
         <v>46286</v>
       </c>
       <c r="P27" s="5" t="s">
@@ -10960,14 +11013,15 @@
         <v>-8</v>
       </c>
       <c r="M28" s="11">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="N28" s="11">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
         <v>285</v>
       </c>
       <c r="O28" s="6">
+        <f>IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P28" s="5" t="s">
@@ -11075,14 +11129,15 @@
         <v>-8</v>
       </c>
       <c r="M29" s="11">
-        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($F29="","",$F29+90-TODAY()))</f>
         <v>-8</v>
       </c>
       <c r="N29" s="11">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
         <v>275</v>
       </c>
       <c r="O29" s="6">
+        <f>IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P29" s="5" t="s">
@@ -11186,14 +11241,15 @@
         <v>-8</v>
       </c>
       <c r="M30" s="11">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
         <v>330</v>
       </c>
       <c r="N30" s="11">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
         <v>330</v>
       </c>
       <c r="O30" s="6">
+        <f>IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P30" s="5" t="s">
@@ -11299,14 +11355,15 @@
         <v>12</v>
       </c>
       <c r="M31" s="11">
-        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+180-TODAY()))</f>
         <v>84</v>
       </c>
       <c r="N31" s="11">
-        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+180-TODAY()))</f>
         <v>84</v>
       </c>
       <c r="O31" s="6">
+        <f>IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",DATE(2026,10,17))</f>
         <v>46312</v>
       </c>
       <c r="P31" s="5" t="s">
@@ -11409,20 +11466,21 @@
       <c r="K32" s="3">
         <v>46272</v>
       </c>
-      <c r="L32" s="11">
+      <c t="str" r="L32" s="11">
         <f ca="1">IF($O32="","",$O32-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="M32" s="11">
-        <f ca="1">IF($C32="","",$C32+180-TODAY())</f>
-        <v>92</v>
-      </c>
-      <c r="N32" s="11">
-        <f ca="1">IF($C32="","",$C32+365-TODAY())</f>
-        <v>277</v>
-      </c>
-      <c r="O32" s="6">
-        <v>46264</v>
+        <v/>
+      </c>
+      <c t="str" r="M32" s="11">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N32" s="11">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O32" s="6">
+        <f>IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",DATE(2026,8,30))</f>
+        <v/>
       </c>
       <c r="P32" s="5" t="s">
         <v>45</v>
@@ -11522,20 +11580,21 @@
       <c r="K33" s="3">
         <v>46276</v>
       </c>
-      <c r="L33" s="11">
+      <c t="str" r="L33" s="11">
         <f ca="1">IF($O33="","",$O33-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="M33" s="11">
-        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>289</v>
-      </c>
-      <c r="N33" s="11">
-        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>289</v>
-      </c>
-      <c r="O33" s="6">
-        <v>46264</v>
+        <v/>
+      </c>
+      <c t="str" r="M33" s="11">
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N33" s="11">
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O33" s="6">
+        <f>IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",DATE(2026,8,30))</f>
+        <v/>
       </c>
       <c r="P33" s="5" t="s">
         <v>45</v>
@@ -11637,20 +11696,21 @@
       <c r="K34" s="3">
         <v>46272</v>
       </c>
-      <c r="L34" s="11">
+      <c t="str" r="L34" s="11">
         <f ca="1">IF($O34="","",$O34-TODAY())</f>
-        <v>-35</v>
-      </c>
-      <c r="M34" s="11">
-        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
-        <v>277</v>
-      </c>
-      <c r="N34" s="11">
-        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
-        <v>277</v>
-      </c>
-      <c r="O34" s="6">
-        <v>46265</v>
+        <v/>
+      </c>
+      <c t="str" r="M34" s="11">
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N34" s="11">
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O34" s="6">
+        <f>IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",DATE(2026,8,31))</f>
+        <v/>
       </c>
       <c r="P34" s="5" t="s">
         <v>45</v>
@@ -11757,14 +11817,15 @@
         <v>-29</v>
       </c>
       <c r="M35" s="11">
-        <f ca="1">IF($F35="","",$F35+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",IF($F35="","",$F35+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="N35" s="11">
-        <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",IF($C35="","",$C35+365-TODAY()))</f>
         <v>346</v>
       </c>
       <c r="O35" s="6">
+        <f>IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P35" s="5" t="s">
@@ -11863,20 +11924,21 @@
       <c r="K36" s="3">
         <v>46272</v>
       </c>
-      <c r="L36" s="11">
+      <c t="str" r="L36" s="11">
         <f ca="1">IF($O36="","",$O36-TODAY())</f>
-        <v>-21</v>
-      </c>
-      <c r="M36" s="11">
-        <f ca="1">IF($C36="","",$C36+180-TODAY())</f>
-        <v>82</v>
-      </c>
-      <c r="N36" s="11">
-        <f ca="1">IF($C36="","",$C36+365-TODAY())</f>
-        <v>267</v>
-      </c>
-      <c r="O36" s="6">
-        <v>46279</v>
+        <v/>
+      </c>
+      <c t="str" r="M36" s="11">
+        <f ca="1">IF(AND(TRIM($A36)="Finalized",$K36&lt;&gt;""),"",IF($C36="","",$C36+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N36" s="11">
+        <f ca="1">IF(AND(TRIM($A36)="Finalized",$K36&lt;&gt;""),"",IF($C36="","",$C36+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O36" s="6">
+        <f>IF(AND(TRIM($A36)="Finalized",$K36&lt;&gt;""),"",DATE(2026,9,14))</f>
+        <v/>
       </c>
       <c r="P36" s="5" t="s">
         <v>45</v>
@@ -11976,20 +12038,21 @@
       <c r="K37" s="3">
         <v>46282</v>
       </c>
-      <c r="L37" s="11">
+      <c t="str" r="L37" s="11">
         <f ca="1">IF($O37="","",$O37-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M37" s="11">
-        <f ca="1">IF($F37="","",$F37+90-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="N37" s="11">
-        <f ca="1">IF($C37="","",$C37+365-TODAY())</f>
-        <v>268</v>
-      </c>
-      <c r="O37" s="6">
-        <v>46281</v>
+        <v/>
+      </c>
+      <c t="str" r="M37" s="11">
+        <f ca="1">IF(AND(TRIM($A37)="Finalized",$K37&lt;&gt;""),"",IF($F37="","",$F37+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N37" s="11">
+        <f ca="1">IF(AND(TRIM($A37)="Finalized",$K37&lt;&gt;""),"",IF($C37="","",$C37+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O37" s="6">
+        <f>IF(AND(TRIM($A37)="Finalized",$K37&lt;&gt;""),"",DATE(2026,9,16))</f>
+        <v/>
       </c>
       <c r="P37" s="5" t="s">
         <v>45</v>
@@ -12087,20 +12150,21 @@
       <c r="K38" s="3">
         <v>46282</v>
       </c>
-      <c r="L38" s="11">
+      <c t="str" r="L38" s="11">
         <f ca="1">IF($O38="","",$O38-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M38" s="11">
-        <f ca="1">IF($C38="","",$C38+180-TODAY())</f>
-        <v>84</v>
-      </c>
-      <c r="N38" s="11">
-        <f ca="1">IF($C38="","",$C38+365-TODAY())</f>
-        <v>269</v>
-      </c>
-      <c r="O38" s="6">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M38" s="11">
+        <f ca="1">IF(AND(TRIM($A38)="Finalized",$K38&lt;&gt;""),"",IF($C38="","",$C38+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N38" s="11">
+        <f ca="1">IF(AND(TRIM($A38)="Finalized",$K38&lt;&gt;""),"",IF($C38="","",$C38+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O38" s="6">
+        <f>IF(AND(TRIM($A38)="Finalized",$K38&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P38" s="5" t="s">
         <v>45</v>
@@ -12202,20 +12266,21 @@
       <c r="K39" s="3">
         <v>46282</v>
       </c>
-      <c r="L39" s="11">
+      <c t="str" r="L39" s="11">
         <f ca="1">IF($O39="","",$O39-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M39" s="11">
-        <f ca="1">IF($C39="","",$C39+365-TODAY())</f>
-        <v>287</v>
-      </c>
-      <c r="N39" s="11">
-        <f ca="1">IF($C39="","",$C39+365-TODAY())</f>
-        <v>287</v>
-      </c>
-      <c r="O39" s="6">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M39" s="11">
+        <f ca="1">IF(AND(TRIM($A39)="Finalized",$K39&lt;&gt;""),"",IF($C39="","",$C39+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N39" s="11">
+        <f ca="1">IF(AND(TRIM($A39)="Finalized",$K39&lt;&gt;""),"",IF($C39="","",$C39+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O39" s="6">
+        <f>IF(AND(TRIM($A39)="Finalized",$K39&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P39" s="5" t="s">
         <v>45</v>
@@ -12317,20 +12382,21 @@
       <c r="K40" s="3">
         <v>46282</v>
       </c>
-      <c r="L40" s="11">
+      <c t="str" r="L40" s="11">
         <f ca="1">IF($O40="","",$O40-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M40" s="11">
-        <f ca="1">IF($F40="","",$F40+90-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="N40" s="11">
-        <f ca="1">IF($C40="","",$C40+365-TODAY())</f>
-        <v>275</v>
-      </c>
-      <c r="O40" s="6">
-        <v>46285</v>
+        <v/>
+      </c>
+      <c t="str" r="M40" s="11">
+        <f ca="1">IF(AND(TRIM($A40)="Finalized",$K40&lt;&gt;""),"",IF($F40="","",$F40+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N40" s="11">
+        <f ca="1">IF(AND(TRIM($A40)="Finalized",$K40&lt;&gt;""),"",IF($C40="","",$C40+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O40" s="6">
+        <f>IF(AND(TRIM($A40)="Finalized",$K40&lt;&gt;""),"",DATE(2026,9,20))</f>
+        <v/>
       </c>
       <c r="P40" s="5" t="s">
         <v>45</v>
@@ -12430,20 +12496,21 @@
       <c r="K41" s="3">
         <v>46243</v>
       </c>
-      <c r="L41" s="11">
+      <c t="str" r="L41" s="11">
         <f ca="1">IF($O41="","",$O41-TODAY())</f>
-        <v>-12</v>
-      </c>
-      <c r="M41" s="11">
-        <f ca="1">IF($F41="","",$F41+90-TODAY())</f>
-        <v>-12</v>
-      </c>
-      <c r="N41" s="11">
-        <f ca="1">IF($C41="","",$C41+365-TODAY())</f>
-        <v>308</v>
-      </c>
-      <c r="O41" s="6">
-        <v>46288</v>
+        <v/>
+      </c>
+      <c t="str" r="M41" s="11">
+        <f ca="1">IF(AND(TRIM($A41)="Finalized",$K41&lt;&gt;""),"",IF($F41="","",$F41+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N41" s="11">
+        <f ca="1">IF(AND(TRIM($A41)="Finalized",$K41&lt;&gt;""),"",IF($C41="","",$C41+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O41" s="6">
+        <f>IF(AND(TRIM($A41)="Finalized",$K41&lt;&gt;""),"",DATE(2026,9,23))</f>
+        <v/>
       </c>
       <c r="P41" s="5" t="s">
         <v>45</v>
@@ -12543,20 +12610,21 @@
       <c r="K42" s="3">
         <v>46283</v>
       </c>
-      <c r="L42" s="11">
+      <c t="str" r="L42" s="11">
         <f ca="1">IF($O42="","",$O42-TODAY())</f>
-        <v>-8</v>
-      </c>
-      <c r="M42" s="11">
-        <f ca="1">IF($C42="","",$C42+180-TODAY())</f>
-        <v>90</v>
-      </c>
-      <c r="N42" s="11">
-        <f ca="1">IF($C42="","",$C42+365-TODAY())</f>
-        <v>275</v>
-      </c>
-      <c r="O42" s="6">
-        <v>46292</v>
+        <v/>
+      </c>
+      <c t="str" r="M42" s="11">
+        <f ca="1">IF(AND(TRIM($A42)="Finalized",$K42&lt;&gt;""),"",IF($C42="","",$C42+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N42" s="11">
+        <f ca="1">IF(AND(TRIM($A42)="Finalized",$K42&lt;&gt;""),"",IF($C42="","",$C42+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O42" s="6">
+        <f>IF(AND(TRIM($A42)="Finalized",$K42&lt;&gt;""),"",DATE(2026,9,27))</f>
+        <v/>
       </c>
       <c r="P42" s="5" t="s">
         <v>45</v>
@@ -12654,20 +12722,21 @@
       <c r="K43" s="3">
         <v>46300</v>
       </c>
-      <c r="L43" s="11">
+      <c t="str" r="L43" s="11">
         <f ca="1">IF($O43="","",$O43-TODAY())</f>
-        <v>-8</v>
-      </c>
-      <c r="M43" s="11">
-        <f ca="1">IF($C43="","",$C43+180-TODAY())</f>
-        <v>169</v>
-      </c>
-      <c r="N43" s="11">
-        <f ca="1">IF($C43="","",$C43+365-TODAY())</f>
-        <v>354</v>
-      </c>
-      <c r="O43" s="6">
-        <v>46292</v>
+        <v/>
+      </c>
+      <c t="str" r="M43" s="11">
+        <f ca="1">IF(AND(TRIM($A43)="Finalized",$K43&lt;&gt;""),"",IF($C43="","",$C43+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N43" s="11">
+        <f ca="1">IF(AND(TRIM($A43)="Finalized",$K43&lt;&gt;""),"",IF($C43="","",$C43+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O43" s="6">
+        <f>IF(AND(TRIM($A43)="Finalized",$K43&lt;&gt;""),"",DATE(2026,9,27))</f>
+        <v/>
       </c>
       <c r="P43" s="5" t="s">
         <v>45</v>
@@ -12733,83 +12802,88 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN43" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L43 O2:O43">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="74" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="2">
+    <cfRule type="expression" dxfId="73" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="3">
+    <cfRule type="expression" dxfId="72" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="4">
+    <cfRule type="expression" dxfId="71" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="5">
+    <cfRule type="expression" dxfId="70" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M43">
-    <cfRule type="expression" dxfId="69" priority="6">
+    <cfRule type="expression" dxfId="69" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="7">
+    <cfRule type="expression" dxfId="68" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="8">
+    <cfRule type="expression" dxfId="67" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="9">
+    <cfRule type="expression" dxfId="66" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="10">
+    <cfRule type="expression" dxfId="65" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N43">
-    <cfRule type="expression" dxfId="64" priority="11">
+    <cfRule type="expression" dxfId="64" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="12">
+    <cfRule type="expression" dxfId="63" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="13">
+    <cfRule type="expression" dxfId="62" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="14">
+    <cfRule type="expression" dxfId="61" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="15">
+    <cfRule type="expression" dxfId="60" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="16">
+    <cfRule type="expression" dxfId="95" priority="17">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="17">
+    <cfRule type="expression" dxfId="96" priority="18">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="18">
+    <cfRule type="expression" dxfId="97" priority="19">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="19">
+    <cfRule type="expression" dxfId="98" priority="20">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="20">
+    <cfRule type="expression" dxfId="99" priority="21">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13020,14 +13094,15 @@
         <v>75</v>
       </c>
       <c r="M2" s="11">
-        <f ca="1">IF($F2="","",$F2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($F2="","",$F2+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="N2" s="11">
-        <f ca="1">IF($F2="","",$F2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($F2="","",$F2+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,12,19))</f>
         <v>46375</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -13133,14 +13208,15 @@
         <v>239</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>105</v>
       </c>
       <c r="N3" s="11">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>290</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,6,1))</f>
         <v>46539</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -13246,14 +13322,15 @@
         <v>267</v>
       </c>
       <c r="M4" s="11" t="str">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N4" s="11" t="str">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,6,29))</f>
         <v>46567</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -13365,14 +13442,15 @@
         <v>-36</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>134</v>
       </c>
       <c r="N5" s="11">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>319</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,8,30))</f>
         <v>46264</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -13484,14 +13562,15 @@
         <v>-29</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>148</v>
       </c>
       <c r="N6" s="11">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>333</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -13603,14 +13682,15 @@
         <v>-29</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v>105</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -13724,14 +13804,15 @@
         <v>-15</v>
       </c>
       <c r="M8" s="11">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+180-TODAY()))</f>
         <v>150</v>
       </c>
       <c r="N8" s="11">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>335</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -13843,14 +13924,15 @@
         <v>-15</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($F9="","",$F9+90-TODAY()))</f>
         <v>-15</v>
       </c>
       <c r="N9" s="11">
-        <f ca="1">IF($C9="","",$C9+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+540-TODAY()))</f>
         <v>480</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,9,20))</f>
         <v>46285</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -13960,14 +14042,15 @@
         <v>-8</v>
       </c>
       <c r="M10" s="11">
-        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($F10="","",$F10+90-TODAY()))</f>
         <v>-8</v>
       </c>
       <c r="N10" s="11">
-        <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+540-TODAY()))</f>
         <v>502</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -14079,14 +14162,15 @@
         <v>-8</v>
       </c>
       <c r="M11" s="11">
-        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+180-TODAY()))</f>
         <v>156</v>
       </c>
       <c r="N11" s="11">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>341</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,9,27))</f>
         <v>46292</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -14190,14 +14274,15 @@
         <v>-66</v>
       </c>
       <c r="M12" s="11">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>288</v>
       </c>
       <c r="N12" s="11">
-        <f ca="1">IF($C12="","",$C12+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+90-TODAY()))</f>
         <v>13</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,7,31))</f>
         <v>46234</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -14311,14 +14396,15 @@
         <v>-36</v>
       </c>
       <c r="M13" s="11">
-        <f ca="1">IF($F13="","",$F13+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($F13="","",$F13+90-TODAY()))</f>
         <v>-36</v>
       </c>
       <c r="N13" s="11">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>268</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,8,30))</f>
         <v>46264</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -14430,14 +14516,15 @@
         <v>-29</v>
       </c>
       <c r="M14" s="11">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
         <v>104</v>
       </c>
       <c r="N14" s="11">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>289</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -14544,20 +14631,21 @@
       <c r="K15" s="3">
         <v>46300</v>
       </c>
-      <c r="L15" s="11">
+      <c t="str" r="L15" s="11">
         <f ca="1">IF($O15="","",$O15-TODAY())</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="11">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>118</v>
-      </c>
-      <c r="N15" s="11">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>118</v>
-      </c>
-      <c r="O15" s="6">
-        <v>46301</v>
+        <v/>
+      </c>
+      <c t="str" r="M15" s="11">
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N15" s="11">
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2026,10,6))</f>
+        <v/>
       </c>
       <c r="P15" s="5" t="s">
         <v>106</v>
@@ -14663,20 +14751,21 @@
       <c r="K16" s="3">
         <v>46300</v>
       </c>
-      <c r="L16" s="11">
+      <c t="str" r="L16" s="11">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>8</v>
-      </c>
-      <c r="M16" s="11">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>118</v>
-      </c>
-      <c r="N16" s="11">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>118</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46308</v>
+        <v/>
+      </c>
+      <c t="str" r="M16" s="11">
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N16" s="11">
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,10,13))</f>
+        <v/>
       </c>
       <c r="P16" s="5" t="s">
         <v>106</v>
@@ -14782,20 +14871,21 @@
       <c r="K17" s="3">
         <v>46300</v>
       </c>
-      <c r="L17" s="11">
+      <c t="str" r="L17" s="11">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>22</v>
-      </c>
-      <c r="M17" s="11">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>118</v>
-      </c>
-      <c r="N17" s="11">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>118</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46322</v>
+        <v/>
+      </c>
+      <c t="str" r="M17" s="11">
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N17" s="11">
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,10,27))</f>
+        <v/>
       </c>
       <c r="P17" s="5" t="s">
         <v>106</v>
@@ -14869,100 +14959,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN17" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L17">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="59" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="2">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="3">
+    <cfRule type="expression" dxfId="57" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="4">
+    <cfRule type="expression" dxfId="56" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="55" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M17">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="54" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="7">
+    <cfRule type="expression" dxfId="53" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="8">
+    <cfRule type="expression" dxfId="52" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="9">
+    <cfRule type="expression" dxfId="51" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="10">
+    <cfRule type="expression" dxfId="50" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N17">
-    <cfRule type="expression" dxfId="49" priority="11">
+    <cfRule type="expression" dxfId="49" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="12">
+    <cfRule type="expression" dxfId="48" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="13">
+    <cfRule type="expression" dxfId="47" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="14">
+    <cfRule type="expression" dxfId="46" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="15">
+    <cfRule type="expression" dxfId="45" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U17">
-    <cfRule type="expression" dxfId="44" priority="16">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="17">
+    <cfRule type="expression" dxfId="43" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="18">
+    <cfRule type="expression" dxfId="42" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="19">
+    <cfRule type="expression" dxfId="41" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="20">
+    <cfRule type="expression" dxfId="40" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15179,14 +15274,15 @@
         <v>2</v>
       </c>
       <c r="M2" s="11">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v>86</v>
       </c>
       <c r="N2" s="11">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v>86</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,10,7))</f>
         <v>46302</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -15292,14 +15388,15 @@
         <v>18</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($F3="","",$F3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+365-TODAY()))</f>
         <v>263</v>
       </c>
       <c r="N3" s="11" t="str">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,10,23))</f>
         <v>46318</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -15405,14 +15502,15 @@
         <v>-29</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="N4" s="11">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>262</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -15520,14 +15618,15 @@
         <v>-26</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($F5="","",$F5+90-TODAY()))</f>
         <v>-26</v>
       </c>
       <c r="N5" s="11">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>262</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,9,9))</f>
         <v>46274</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -15627,14 +15726,15 @@
         <v>52</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($F6="","",$F6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+365-TODAY()))</f>
         <v>267</v>
       </c>
       <c r="N6" s="11">
-        <f ca="1">IF($F6="","",$F6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+365-TODAY()))</f>
         <v>267</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,11,26))</f>
         <v>46352</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -15732,14 +15832,15 @@
         <v>75</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($F7="","",$F7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($F7="","",$F7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,12,19))</f>
         <v>46375</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -15843,14 +15944,15 @@
         <v>242</v>
       </c>
       <c r="M8" s="11">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>253</v>
       </c>
       <c r="N8" s="11">
-        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+120-TODAY()))</f>
         <v>8</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2027,6,4))</f>
         <v>46542</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -15950,14 +16052,15 @@
         <v>253</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>260</v>
       </c>
       <c r="N9" s="11">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+120-TODAY()))</f>
         <v>15</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2027,6,15))</f>
         <v>46553</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -16057,14 +16160,15 @@
         <v>256</v>
       </c>
       <c r="M10" s="11">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>283</v>
       </c>
       <c r="N10" s="11">
-        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+120-TODAY()))</f>
         <v>38</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2027,6,18))</f>
         <v>46556</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -16350,14 +16454,15 @@
         <v>-36</v>
       </c>
       <c r="M13" s="11">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+180-TODAY()))</f>
         <v>136</v>
       </c>
       <c r="N13" s="11">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>321</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,8,30))</f>
         <v>46264</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -16465,14 +16570,15 @@
         <v>-33</v>
       </c>
       <c r="M14" s="11">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
         <v>134</v>
       </c>
       <c r="N14" s="11">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>319</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,9,2))</f>
         <v>46267</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -16580,14 +16686,15 @@
         <v>-29</v>
       </c>
       <c r="M15" s="11" t="str">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N15" s="11" t="str">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -16697,14 +16804,15 @@
         <v>-29</v>
       </c>
       <c r="M16" s="11">
-        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($F16="","",$F16+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="N16" s="11">
-        <f ca="1">IF($C16="","",$C16+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+540-TODAY()))</f>
         <v>476</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,9,6))</f>
         <v>46271</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -16816,14 +16924,15 @@
         <v>-25</v>
       </c>
       <c r="M17" s="11">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+180-TODAY()))</f>
         <v>77</v>
       </c>
       <c r="N17" s="11">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>262</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,9,10))</f>
         <v>46275</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -16925,14 +17034,15 @@
         <v>-19</v>
       </c>
       <c r="M18" s="11" t="str">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N18" s="11" t="str">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -17040,14 +17150,15 @@
         <v>-13</v>
       </c>
       <c r="M19" s="11">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+180-TODAY()))</f>
         <v>152</v>
       </c>
       <c r="N19" s="11">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v>337</v>
       </c>
       <c r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,9,22))</f>
         <v>46287</v>
       </c>
       <c r="P19" s="5" t="s">
@@ -17151,14 +17262,15 @@
         <v>-12</v>
       </c>
       <c r="M20" s="11" t="str">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N20" s="11" t="str">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P20" s="5" t="s">
@@ -17268,14 +17380,15 @@
         <v>-12</v>
       </c>
       <c r="M21" s="11">
-        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+180-TODAY()))</f>
         <v>90</v>
       </c>
       <c r="N21" s="11">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+365-TODAY()))</f>
         <v>275</v>
       </c>
       <c r="O21" s="6">
+        <f>IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P21" s="5" t="s">
@@ -17383,14 +17496,15 @@
         <v>-7</v>
       </c>
       <c r="M22" s="11">
-        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($F22="","",$F22+90-TODAY()))</f>
         <v>-7</v>
       </c>
       <c r="N22" s="11">
-        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+180-TODAY()))</f>
         <v>103</v>
       </c>
       <c r="O22" s="6">
+        <f>IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",DATE(2026,9,28))</f>
         <v>46293</v>
       </c>
       <c r="P22" s="5" t="s">
@@ -17496,14 +17610,15 @@
         <v>-7</v>
       </c>
       <c r="M23" s="11">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+365-TODAY()))</f>
         <v>330</v>
       </c>
       <c r="N23" s="11">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+365-TODAY()))</f>
         <v>330</v>
       </c>
       <c r="O23" s="6">
+        <f>IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",DATE(2026,9,28))</f>
         <v>46293</v>
       </c>
       <c r="P23" s="5" t="s">
@@ -17602,20 +17717,21 @@
       <c r="K24" s="3">
         <v>46246</v>
       </c>
-      <c r="L24" s="11">
+      <c t="str" r="L24" s="11">
         <f ca="1">IF($O24="","",$O24-TODAY())</f>
-        <v>-50</v>
-      </c>
-      <c r="M24" s="11">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>297</v>
-      </c>
-      <c r="N24" s="11">
-        <f ca="1">IF($C24="","",$C24+90-TODAY())</f>
-        <v>22</v>
-      </c>
-      <c r="O24" s="6">
-        <v>46250</v>
+        <v/>
+      </c>
+      <c t="str" r="M24" s="11">
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N24" s="11">
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O24" s="6">
+        <f>IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",DATE(2026,8,16))</f>
+        <v/>
       </c>
       <c r="P24" s="5" t="s">
         <v>119</v>
@@ -17711,20 +17827,21 @@
       <c r="K25" s="3">
         <v>46271</v>
       </c>
-      <c r="L25" s="11">
+      <c t="str" r="L25" s="11">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>-26</v>
-      </c>
-      <c r="M25" s="11">
-        <f ca="1">IF($F25="","",$F25+90-TODAY())</f>
-        <v>-26</v>
-      </c>
-      <c r="N25" s="11">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>261</v>
-      </c>
-      <c r="O25" s="6">
-        <v>46274</v>
+        <v/>
+      </c>
+      <c t="str" r="M25" s="11">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($F25="","",$F25+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N25" s="11">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O25" s="6">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2026,9,9))</f>
+        <v/>
       </c>
       <c r="P25" s="5" t="s">
         <v>45</v>
@@ -17826,20 +17943,21 @@
       <c r="K26" s="3">
         <v>46300</v>
       </c>
-      <c r="L26" s="11">
+      <c t="str" r="L26" s="11">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>13</v>
-      </c>
-      <c r="M26" s="11">
-        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
-        <v>97</v>
-      </c>
-      <c r="N26" s="11">
-        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
-        <v>97</v>
-      </c>
-      <c r="O26" s="6">
-        <v>46313</v>
+        <v/>
+      </c>
+      <c t="str" r="M26" s="11">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N26" s="11">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O26" s="6">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2026,10,18))</f>
+        <v/>
       </c>
       <c r="P26" s="5" t="s">
         <v>106</v>
@@ -17907,100 +18025,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN26" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L26">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="3">
+    <cfRule type="expression" dxfId="37" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="36" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="5">
+    <cfRule type="expression" dxfId="35" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M26">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="34" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="7">
+    <cfRule type="expression" dxfId="33" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="8">
+    <cfRule type="expression" dxfId="32" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="31" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="10">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N26">
-    <cfRule type="expression" dxfId="29" priority="11">
+    <cfRule type="expression" dxfId="29" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="13">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="14">
+    <cfRule type="expression" dxfId="26" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="15">
+    <cfRule type="expression" dxfId="25" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O26">
-    <cfRule type="expression" dxfId="24" priority="16">
+    <cfRule type="expression" dxfId="24" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="23" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18211,14 +18334,15 @@
         <v>240</v>
       </c>
       <c r="M2" s="11">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>267</v>
       </c>
       <c r="N2" s="11">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+120-TODAY()))</f>
         <v>22</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2027,6,2))</f>
         <v>46540</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -18318,14 +18442,15 @@
         <v>254</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>267</v>
       </c>
       <c r="N3" s="11">
-        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+120-TODAY()))</f>
         <v>22</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,6,16))</f>
         <v>46554</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -18425,14 +18550,15 @@
         <v>256</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>277</v>
       </c>
       <c r="N4" s="11">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>32</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,6,18))</f>
         <v>46556</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -18535,7 +18661,7 @@
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="O5" s="6"/>
@@ -18633,7 +18759,7 @@
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="O6" s="6"/>
@@ -18732,14 +18858,15 @@
         <v>-34</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+90-TODAY()))</f>
         <v>-34</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v>83</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,9,1))</f>
         <v>46266</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -18843,14 +18970,15 @@
         <v>-33</v>
       </c>
       <c r="M8" s="11" t="str">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N8" s="11" t="str">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,9,2))</f>
         <v>46267</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -18954,14 +19082,15 @@
         <v>-28</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+180-TODAY()))</f>
         <v>127</v>
       </c>
       <c r="N9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>312</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,9,7))</f>
         <v>46272</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -19069,14 +19198,15 @@
         <v>-27</v>
       </c>
       <c r="M10" s="11">
-        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($F10="","",$F10+90-TODAY()))</f>
         <v>-27</v>
       </c>
       <c r="N10" s="11">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>269</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,9,8))</f>
         <v>46273</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -19178,14 +19308,15 @@
         <v>-12</v>
       </c>
       <c r="M11" s="11" t="str">
-        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N11" s="11" t="str">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -19287,14 +19418,15 @@
         <v>-7</v>
       </c>
       <c r="M12" s="11">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+180-TODAY()))</f>
         <v>160</v>
       </c>
       <c r="N12" s="11">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>345</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,9,28))</f>
         <v>46293</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -19400,14 +19532,15 @@
         <v>11</v>
       </c>
       <c r="M13" s="11">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>302</v>
       </c>
       <c r="N13" s="11">
-        <f ca="1">IF($C13="","",$C13+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+90-TODAY()))</f>
         <v>27</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,10,16))</f>
         <v>46311</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -19504,20 +19637,21 @@
       <c r="K14" s="3">
         <v>46284</v>
       </c>
-      <c r="L14" s="11">
+      <c t="str" r="L14" s="11">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
-        <v>-34</v>
-      </c>
-      <c r="M14" s="11">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>153</v>
-      </c>
-      <c r="N14" s="11">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>338</v>
-      </c>
-      <c r="O14" s="6">
-        <v>46266</v>
+        <v/>
+      </c>
+      <c t="str" r="M14" s="11">
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N14" s="11">
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,9,1))</f>
+        <v/>
       </c>
       <c r="P14" s="5" t="s">
         <v>45</v>
@@ -19619,20 +19753,21 @@
       <c r="K15" s="3">
         <v>46282</v>
       </c>
-      <c r="L15" s="11">
+      <c t="str" r="L15" s="11">
         <f ca="1">IF($O15="","",$O15-TODAY())</f>
-        <v>-20</v>
-      </c>
-      <c r="M15" s="11">
-        <f ca="1">IF($F15="","",$F15+90-TODAY())</f>
-        <v>-20</v>
-      </c>
-      <c r="N15" s="11">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>82</v>
-      </c>
-      <c r="O15" s="6">
-        <v>46280</v>
+        <v/>
+      </c>
+      <c t="str" r="M15" s="11">
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($F15="","",$F15+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N15" s="11">
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2026,9,15))</f>
+        <v/>
       </c>
       <c r="P15" s="5" t="s">
         <v>45</v>
@@ -19732,20 +19867,21 @@
       <c r="K16" s="3">
         <v>46300</v>
       </c>
-      <c r="L16" s="11">
+      <c t="str" r="L16" s="11">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>10</v>
-      </c>
-      <c r="M16" s="11">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>107</v>
-      </c>
-      <c r="N16" s="11">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>107</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46310</v>
+        <v/>
+      </c>
+      <c t="str" r="M16" s="11">
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N16" s="11">
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,10,15))</f>
+        <v/>
       </c>
       <c r="P16" s="5" t="s">
         <v>106</v>
@@ -19843,20 +19979,21 @@
       <c r="K17" s="3">
         <v>46261</v>
       </c>
-      <c r="L17" s="11">
+      <c t="str" r="L17" s="11">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>-56</v>
-      </c>
-      <c r="M17" s="11">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>263</v>
-      </c>
-      <c r="N17" s="11">
-        <f ca="1">IF($C17="","",$C17+90-TODAY())</f>
-        <v>-12</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46244</v>
+        <v/>
+      </c>
+      <c t="str" r="M17" s="11">
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N17" s="11">
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,8,10))</f>
+        <v/>
       </c>
       <c r="P17" s="5" t="s">
         <v>119</v>
@@ -19960,20 +20097,21 @@
       <c r="K18" s="3">
         <v>46288</v>
       </c>
-      <c r="L18" s="11">
+      <c t="str" r="L18" s="11">
         <f ca="1">IF($O18="","",$O18-TODAY())</f>
-        <v>-28</v>
-      </c>
-      <c r="M18" s="11">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>343</v>
-      </c>
-      <c r="N18" s="11">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>343</v>
-      </c>
-      <c r="O18" s="6">
-        <v>46272</v>
+        <v/>
+      </c>
+      <c t="str" r="M18" s="11">
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N18" s="11">
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,9,7))</f>
+        <v/>
       </c>
       <c r="P18" s="5" t="s">
         <v>45</v>
@@ -20039,100 +20177,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN18" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L18">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M18">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N18">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="13">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O18">
-    <cfRule type="expression" dxfId="4" priority="16">
+    <cfRule type="expression" dxfId="4" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20192,13 +20335,13 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="str">
         <f>"    1 - Due in 5 days or less: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;=0",BH!$L$2:$L$1000,"&lt;=5"),COUNTIFS(DME!$L$2:$L$1000,"&gt;=0",DME!$L$2:$L$1000,"&lt;=5"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;=0",GAE!$L$2:$L$1000,"&lt;=5"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;=0",ORTHO!$L$2:$L$1000,"&lt;=5"),COUNTIFS(US!$L$2:$L$1000,"&gt;=0",US!$L$2:$L$1000,"&lt;=5"))</f>
-        <v>    1 - Due in 5 days or less: 1</v>
+        <v>    1 - Due in 5 days or less: 0</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="str">
         <f>"    2 - Due in 6-30 days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;5",BH!$L$2:$L$1000,"&lt;=30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;5",DME!$L$2:$L$1000,"&lt;=30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;5",GAE!$L$2:$L$1000,"&lt;=30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;5",ORTHO!$L$2:$L$1000,"&lt;=30"),COUNTIFS(US!$L$2:$L$1000,"&gt;5",US!$L$2:$L$1000,"&lt;=30"))</f>
-        <v>    2 - Due in 6-30 days: 7</v>
+        <v>    2 - Due in 6-30 days: 4</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -20210,12 +20353,12 @@
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
         <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
-        <v>    4 - Past deadline: 76</v>
+        <v>    4 - Past deadline: 54</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="str">
-        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <f>"    5 - No limit on file: "&amp;SUM(SUMPRODUCT((BH!$D$2:$D$1000&lt;&gt;"")*(BH!$L$2:$L$1000="")*(1-(TRIM(BH!$A$2:$A$1000)="Finalized")*(BH!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((DME!$D$2:$D$1000&lt;&gt;"")*(DME!$L$2:$L$1000="")*(1-(TRIM(DME!$A$2:$A$1000)="Finalized")*(DME!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((GAE!$D$2:$D$1000&lt;&gt;"")*(GAE!$L$2:$L$1000="")*(1-(TRIM(GAE!$A$2:$A$1000)="Finalized")*(GAE!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((ORTHO!$D$2:$D$1000&lt;&gt;"")*(ORTHO!$L$2:$L$1000="")*(1-(TRIM(ORTHO!$A$2:$A$1000)="Finalized")*(ORTHO!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((US!$D$2:$D$1000&lt;&gt;"")*(US!$L$2:$L$1000="")*(1-(TRIM(US!$A$2:$A$1000)="Finalized")*(US!$K$2:$K$1000&lt;&gt;""))))</f>
         <v>    5 - No limit on file: 15</v>
       </c>
     </row>
